--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_hazelnut_small.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_hazelnut_small.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12.58316588401794</v>
+        <v>12.21319556236267</v>
       </c>
       <c r="D2" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E2" t="n">
-        <v>0.038155160844326</v>
+        <v>0.2169700711965561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.862500011920929</v>
+        <v>0.8387096524238586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8695651888847351</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3694162368774414</v>
+        <v>0.2783425152301788</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0704226568341255</v>
+        <v>0.0163346268913962</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0565090999007225</v>
+        <v>0.0547459905797785</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0189764882578994</v>
+        <v>0.0426668188788674</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0797599293968894</v>
+        <v>5.390426874160767</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0661415894826253</v>
+        <v>18.0661768913269</v>
       </c>
       <c r="O2" t="n">
-        <v>6.262241125106812</v>
-      </c>
-      <c r="P2" t="n">
-        <v>26.32077670097351</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>21.82672452926636</v>
+        <v>14.08005023002624</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-162640</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-154135</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>12.38744211196899</v>
+        <v>12.18361353874206</v>
       </c>
       <c r="D3" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0443068295717239</v>
+        <v>0.1989501863718032</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8985507488250732</v>
+        <v>0.8552631735801697</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8794326186180115</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.366029679775238</v>
+        <v>0.2787506282329559</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06883324682712549</v>
+        <v>0.0164635513768051</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0566728338599205</v>
+        <v>0.0547269496050747</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0187001054937189</v>
+        <v>0.0423588947816328</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0780866637374415</v>
+        <v>5.432971954345703</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06545339569900969</v>
+        <v>18.05989336967468</v>
       </c>
       <c r="O3" t="n">
-        <v>6.171034812927246</v>
-      </c>
-      <c r="P3" t="n">
-        <v>25.76859903335572</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>21.59962058067322</v>
+        <v>13.97843527793884</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-162844</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-154321</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>12.43207240104675</v>
+        <v>12.26745891571045</v>
       </c>
       <c r="D4" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0401036031544208</v>
+        <v>0.2029995024204254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9251700639724731</v>
+        <v>0.91780823469162</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926174521446228</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3623062372207641</v>
+        <v>0.2809678912162781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0672120526432991</v>
+        <v>0.0166956359689885</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05617630854249</v>
+        <v>0.055516649015022</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0184444918777003</v>
+        <v>0.0434840122858683</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07628534779404141</v>
+        <v>5.509559869766235</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0650226282350944</v>
+        <v>18.32049417495728</v>
       </c>
       <c r="O4" t="n">
-        <v>6.086682319641113</v>
-      </c>
-      <c r="P4" t="n">
-        <v>25.17416477203369</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>21.45746731758118</v>
+        <v>14.34972405433655</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-163048</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-154506</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>12.43588304519653</v>
+        <v>12.28580522537231</v>
       </c>
       <c r="D5" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0390609875321388</v>
+        <v>0.2181570380926132</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9103448390960692</v>
+        <v>0.8767123222351074</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9103448390960692</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3622830212116241</v>
+        <v>0.2915711402893066</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0705301463603973</v>
+        <v>0.0169231790484804</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0570480711758136</v>
+        <v>0.0564340353012084</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01826290361809</v>
+        <v>0.0432316765640721</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0799161687041773</v>
+        <v>5.584649085998535</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0663714488347371</v>
+        <v>18.6232316493988</v>
       </c>
       <c r="O5" t="n">
-        <v>6.026758193969727</v>
-      </c>
-      <c r="P5" t="n">
-        <v>26.37233567237854</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21.90257811546326</v>
+        <v>14.2664532661438</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-163253</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-154653</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>12.61450529098511</v>
+        <v>12.18093872070312</v>
       </c>
       <c r="D6" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0423964858055114</v>
+        <v>0.2147834002971649</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8513513803482056</v>
+        <v>0.8873239159584045</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8456375598907471</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3614508211612701</v>
+        <v>0.2778027057647705</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06903939694166179</v>
+        <v>0.0164419441512136</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0580211281776428</v>
+        <v>0.0555733608477043</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0184745593504472</v>
+        <v>0.0430214094393181</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07815835331425521</v>
+        <v>5.425841569900513</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0672047008167613</v>
+        <v>18.33920907974243</v>
       </c>
       <c r="O6" t="n">
-        <v>6.096604585647583</v>
-      </c>
-      <c r="P6" t="n">
-        <v>25.79225659370422</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>22.17755126953125</v>
+        <v>14.19706511497498</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-163458</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-154839</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>35.37113499641418</v>
+        <v>235.287570476532</v>
       </c>
       <c r="D2" t="n">
-        <v>1.730000019073486</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0615864403545856</v>
+        <v>0.2104155700653791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9402984976768494</v>
+        <v>0.9473684430122375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9305555820465088</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1779724508523941</v>
+        <v>0.2689106464385986</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0621134452521801</v>
+        <v>0.0156713254523999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0512138120830059</v>
+        <v>0.0458406014875932</v>
       </c>
       <c r="L2" t="n">
-        <v>0.012491894490791</v>
+        <v>0.0356199806386774</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0709668188384085</v>
+        <v>5.171537399291992</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0602595495455192</v>
+        <v>15.12739849090576</v>
       </c>
       <c r="O2" t="n">
-        <v>4.12232518196106</v>
-      </c>
-      <c r="P2" t="n">
-        <v>23.4190502166748</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19.88565135002136</v>
+        <v>11.75459361076355</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250715-235948</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-170205</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>33.57688784599304</v>
+        <v>281.9653375148773</v>
       </c>
       <c r="D3" t="n">
-        <v>1.860000014305115</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0810296729207038</v>
+        <v>0.2095452290156791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8414633870124817</v>
+        <v>0.935251772403717</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7865168452262878</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1993263363838195</v>
+        <v>0.2628549933433532</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0622135661542415</v>
+        <v>0.0155228491985436</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0517671704292297</v>
+        <v>0.0460620005925496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0131106051531705</v>
+        <v>0.0356018153103915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0724911147897893</v>
+        <v>5.122540235519409</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0626719424218842</v>
+        <v>15.20046019554138</v>
       </c>
       <c r="O3" t="n">
-        <v>4.326499700546265</v>
-      </c>
-      <c r="P3" t="n">
-        <v>23.92206788063049</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>20.6817409992218</v>
+        <v>11.7485990524292</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250716-000529</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-170408</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>35.46189737319946</v>
+        <v>216.0969274044037</v>
       </c>
       <c r="D4" t="n">
-        <v>1.759999990463257</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08066663444042201</v>
+        <v>0.2112238881262865</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8970588445663452</v>
+        <v>0.9428571462631226</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8936170339584351</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1744603216648101</v>
+        <v>0.2654210031032562</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0618226751685142</v>
+        <v>0.0155207034313317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0514764711260795</v>
+        <v>0.045778675512834</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0129121014566132</v>
+        <v>0.0355526931358106</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0708780888355139</v>
+        <v>5.121832132339478</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0607312383073748</v>
+        <v>15.10696291923523</v>
       </c>
       <c r="O4" t="n">
-        <v>4.260993480682373</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.3897693157196</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>20.04130864143372</v>
+        <v>11.7323887348175</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250716-001156</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-170609</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>35.50421619415283</v>
+        <v>265.2848546504974</v>
       </c>
       <c r="D5" t="n">
-        <v>1.730000019073486</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0803517147898673</v>
+        <v>0.2125723384044788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.919708013534546</v>
+        <v>0.964028775691986</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9027777910232544</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1718959361314773</v>
+        <v>0.2665373384952545</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0613191835582256</v>
+        <v>0.0155653635660807</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0493282563984394</v>
+        <v>0.0459394064816561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0126255273818969</v>
+        <v>0.0358919201475201</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07003636504664559</v>
+        <v>5.136569976806641</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0584424437898578</v>
+        <v>15.16000413894653</v>
       </c>
       <c r="O5" t="n">
-        <v>4.166424036026001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.11200046539306</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19.28600645065308</v>
+        <v>11.84433364868164</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250716-001717</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-170812</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>35.13062143325806</v>
+        <v>234.9698133468628</v>
       </c>
       <c r="D6" t="n">
-        <v>1.759999990463257</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07394615784287439</v>
+        <v>0.2130284445981184</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9103448390960692</v>
+        <v>0.9714285731315612</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9006622433662415</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7387387156486511</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1884284764528274</v>
+        <v>0.263766884803772</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0617534257471561</v>
+        <v>0.0154735261743718</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0514932945370674</v>
+        <v>0.04601427786278</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0130323894096143</v>
+        <v>0.0355962738846287</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0708116141232577</v>
+        <v>5.106263637542725</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0609833825718272</v>
+        <v>15.18471169471741</v>
       </c>
       <c r="O6" t="n">
-        <v>4.300688505172729</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23.36783266067505</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>20.124516248703</v>
+        <v>11.74677038192749</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250716-002328</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-171013</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>mvtec_hazelnut_small</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1175.440788507462</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.159999847412109</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2431679194297023</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.91780823469162</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3722849190235138</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0213299505638353</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0800124731930819</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0723004868536284</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.038883686065674</v>
+      </c>
+      <c r="N2" t="n">
+        <v>26.40411615371704</v>
+      </c>
+      <c r="O2" t="n">
+        <v>23.85916066169739</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-202536</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mvtec_hazelnut_small</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1177.340222597122</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.170000076293945</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2347990117180886</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9115646481513976</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4212199747562408</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0224308743621363</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0793539567427201</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0722269094351566</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.402188539505005</v>
+      </c>
+      <c r="N3" t="n">
+        <v>26.18680572509766</v>
+      </c>
+      <c r="O3" t="n">
+        <v>23.83488011360168</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-204727</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mvtec_hazelnut_small</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1159.995537519455</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.010000228881836</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.243012552584835</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.887417197227478</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3363387584686279</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0193858674078276</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07927062005707711</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0701373172528816</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6.39733624458313</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26.15930461883545</v>
+      </c>
+      <c r="O4" t="n">
+        <v>23.14531469345093</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-210920</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mvtec_hazelnut_small</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1164.323909282684</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.300000190734863</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2398655868355353</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8888888955116272</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4135499894618988</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0226275133364128</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.07793197776332041</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.07136637080799441</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.467079401016235</v>
+      </c>
+      <c r="N5" t="n">
+        <v>25.71755266189575</v>
+      </c>
+      <c r="O5" t="n">
+        <v>23.55090236663818</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-213034</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>mvtec_hazelnut_small</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1168.683113336563</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.235269704955307</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9054054021835328</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3532862067222595</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0199849699482773</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0791795448823408</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0713141744787042</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.595040082931519</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26.12924981117249</v>
+      </c>
+      <c r="O6" t="n">
+        <v>23.53367757797241</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-215212</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_hazelnut_small</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_hazelnut_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
